--- a/docs/StructureDefinition-CPMVitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-CPMVitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-CPMVitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-CPMVitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-CPMVitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-CPMVitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -886,7 +886,7 @@
     <t>FiveWs.status</t>
   </si>
   <si>
-    <t>656: transform using "entered-in-error" on GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (#120.5-4) case not null</t>
+    <t>656: transform using #entered-in-error on GMRV VITAL MEASUREMENT - REASON ENTERED IN ERROR (#120.5-4) case not null</t>
   </si>
   <si>
     <t>Observation.category</t>
@@ -2503,8 +2503,8 @@
     <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="117.9140625" customWidth="true" bestFit="true"/>
-    <col min="44" max="44" width="117.9140625" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="117.765625" customWidth="true" bestFit="true"/>
+    <col min="44" max="44" width="117.765625" customWidth="true" bestFit="true"/>
     <col min="45" max="45" width="44.85546875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/docs/StructureDefinition-CPMVitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-CPMVitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-CPMVitalSignsObservation.xlsx
+++ b/docs/StructureDefinition-CPMVitalSignsObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA GMRV VITAL MEASUREMENT (file 120.5) to FHIR Observation</t>
+    <t>This StructureDefinition contains the maps for VistA file GMRV VITAL MEASUREMENT (#120.5) to VitalSignsObservation</t>
   </si>
   <si>
     <t>Purpose</t>
